--- a/outputs/evaluation/requirement/design/v1/CF_M08/first/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M08/first/CF_M08_req_eval.xlsx
@@ -627,10 +627,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.3158</v>
       </c>
     </row>
   </sheetData>
@@ -763,6 +761,14 @@
           <t>The system shall allow users to register as either a donor or a company.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -776,6 +782,10 @@
           <t>A user can be both a donor and a company.</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,6 +816,14 @@
           <t>The system shall allow logged-in users to view company profiles and their products.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -819,6 +837,10 @@
           <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -849,11 +871,14 @@
           <t>Compatibility tests demonstrating functionality on major browsers and mobile devices.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -867,11 +892,14 @@
           <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M08_R25</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,11 +930,14 @@
           <t>Verify that only the company user can access their products/routes/profile.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_19</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -920,11 +951,14 @@
           <t>Verify that only Business Users can access their products/routes/profile.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M08_R29</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -955,6 +989,14 @@
           <t>A company shall be able to modify its public profile and preview it while editing.</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -968,6 +1010,10 @@
           <t>A company must be able to modify its public profile/page at any time and preview it while editing</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -998,11 +1044,14 @@
           <t>The system shall be available in both Spanish and English (verified by a translator).</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1016,11 +1065,14 @@
           <t>The system should support Spanish and English (verified by a translator).</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M08_R15</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1051,6 +1103,14 @@
           <t>A company shall be able to register a route to link it to its products.</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1064,6 +1124,10 @@
           <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1094,6 +1158,14 @@
           <t>The system shall authenticate existing users via email.</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1107,6 +1179,10 @@
           <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1142,6 +1218,13 @@
           <t>C_03</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1160,11 +1243,9 @@
           <t>CF_M08_C03</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1195,6 +1276,14 @@
           <t>A company shall be able to register a product to be visible on its public profile.</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1208,6 +1297,10 @@
           <t>A company must be able to register a product and have it visible on its profile/page public.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1243,6 +1336,13 @@
           <t>C_04</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1261,6 +1361,9 @@
           <t>CF_M08_C04</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1291,6 +1394,14 @@
           <t>A user shall be able to return a product registered by a company using its routes.</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1304,6 +1415,10 @@
           <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1334,11 +1449,14 @@
           <t>The system must pass security audits without critical vulnerabilities.</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_13</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1352,11 +1470,14 @@
           <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M08_R19</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1387,11 +1508,14 @@
           <t>Usability testing with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1405,11 +1529,14 @@
           <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M08_R17</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1445,6 +1572,13 @@
           <t>C_05</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1463,11 +1597,9 @@
           <t>CF_M08_C06</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1498,11 +1630,14 @@
           <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery tests meeting the specified recovery time.</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1516,11 +1651,14 @@
           <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M08_R21</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1551,6 +1689,14 @@
           <t>Products/routes/profile of a company can only be editable and accessible by that company.</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Changed from QR to Constraint</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1569,11 +1715,9 @@
           <t>CF_M08_C08</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1609,6 +1753,13 @@
           <t>C_01</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1627,11 +1778,9 @@
           <t>CF_M08_C01</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1667,6 +1816,13 @@
           <t>C_02</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1685,11 +1841,9 @@
           <t>CF_M08_C02</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
